--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -1210,79 +1210,79 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-27</v>
+        <v>-122</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>7</v>
+        <v>-28</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>-64</v>
+        <v>-105</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>-42</v>
+        <v>-16</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>11</v>
+        <v>-19</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>-35</v>
+        <v>-40</v>
       </c>
       <c r="K13" s="10" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L13" s="10" t="n">
-        <v>-17</v>
+        <v>-15</v>
       </c>
       <c r="M13" s="10" t="n">
-        <v>-52</v>
+        <v>-36</v>
       </c>
       <c r="N13" s="10" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="O13" s="10" t="n">
-        <v>-22</v>
+        <v>-25</v>
       </c>
       <c r="P13" s="10" t="n">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="Q13" s="10" t="n">
-        <v>-80</v>
+        <v>-72</v>
       </c>
       <c r="R13" s="10" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="S13" s="10" t="n">
-        <v>-46</v>
+        <v>-41</v>
       </c>
       <c r="T13" s="10" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="U13" s="10" t="n">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="V13" s="10" t="n">
         <v>-25</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-80</v>
+        <v>-122</v>
       </c>
       <c r="X13" s="10" t="n">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="Y13" s="11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="14">
@@ -1292,73 +1292,73 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>86</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J14" s="5" t="n">
         <v>72</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="M14" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>83</v>
+      </c>
+      <c r="O14" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="P14" s="5" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q14" s="5" t="n">
         <v>70</v>
       </c>
-      <c r="N14" s="5" t="n">
-        <v>87</v>
-      </c>
-      <c r="O14" s="5" t="n">
-        <v>71</v>
-      </c>
-      <c r="P14" s="5" t="n">
-        <v>86</v>
-      </c>
-      <c r="Q14" s="5" t="n">
-        <v>65</v>
-      </c>
       <c r="R14" s="5" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S14" s="5" t="n">
         <v>72</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="U14" s="5" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="V14" s="5" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="W14" s="5" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="X14" s="5" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Y14" s="12" t="n">
         <v>77</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-122</v>
+        <v>10</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>40</v>
@@ -1273,7 +1273,7 @@
         <v>-25</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-122</v>
+        <v>-105</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>101</v>
@@ -1282,7 +1282,7 @@
         <v>2</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>86</v>
@@ -1364,7 +1364,7 @@
         <v>77</v>
       </c>
       <c r="Z14" s="5" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -1210,79 +1210,79 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>10</v>
+        <v>-92</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>-28</v>
+        <v>-30</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>-105</v>
+        <v>-115</v>
       </c>
       <c r="G13" s="10" t="n">
+        <v>-26</v>
+      </c>
+      <c r="H13" s="10" t="n">
         <v>-16</v>
       </c>
-      <c r="H13" s="10" t="n">
-        <v>-19</v>
-      </c>
       <c r="I13" s="10" t="n">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>-40</v>
+        <v>-42</v>
       </c>
       <c r="K13" s="10" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="L13" s="10" t="n">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="M13" s="10" t="n">
-        <v>-36</v>
+        <v>-34</v>
       </c>
       <c r="N13" s="10" t="n">
         <v>42</v>
       </c>
       <c r="O13" s="10" t="n">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="P13" s="10" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="Q13" s="10" t="n">
-        <v>-72</v>
+        <v>-78</v>
       </c>
       <c r="R13" s="10" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="S13" s="10" t="n">
-        <v>-41</v>
+        <v>-44</v>
       </c>
       <c r="T13" s="10" t="n">
         <v>14</v>
       </c>
       <c r="U13" s="10" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="V13" s="10" t="n">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-105</v>
+        <v>-115</v>
       </c>
       <c r="X13" s="10" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="Y13" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="14">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>86</v>
@@ -1364,7 +1364,7 @@
         <v>77</v>
       </c>
       <c r="Z14" s="5" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-92</v>
+        <v>-152</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-115</v>
+        <v>-152</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="14">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>86</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-152</v>
+        <v>-160</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-152</v>
+        <v>-160</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>86</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-160</v>
+        <v>-302</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-160</v>
+        <v>-302</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-4</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="14">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>86</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="HDD Matrix" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HDD Matrix" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HDD Matrix" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="HDD Matrix" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-160</v>
+        <v>-181</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-160</v>
+        <v>-181</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="14">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>86</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-181</v>
+        <v>-303</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-181</v>
+        <v>-303</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-5</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="14">

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="HDD Matrix" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HDD Matrix" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-303</v>
+        <v>-205</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-303</v>
+        <v>-205</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-11</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="14">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>86</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HDD Matrix" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="HDD Matrix" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-205</v>
+        <v>-184</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-205</v>
+        <v>-184</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="14">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>86</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-184</v>
+        <v>-302</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-184</v>
+        <v>-302</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-5</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="14">

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-302</v>
+        <v>-169</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-302</v>
+        <v>-169</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-11</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="14">

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-169</v>
+        <v>-276</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-169</v>
+        <v>-276</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-4</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="14">

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HDD Matrix" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="HDD Matrix" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-205</v>
+        <v>-276</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-205</v>
+        <v>-276</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-6</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="14">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>86</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-276</v>
+        <v>-168</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-276</v>
+        <v>-168</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-9</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="14">

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="HDD Matrix" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HDD Matrix" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-168</v>
+        <v>-75</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-168</v>
+        <v>-115</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>86</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1</v>
+        <v>0.9867549668874173</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>1</v>
+        <v>0.9867549668874173</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.00157678965626</v>
+        <v>1.000946073793756</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-75</v>
+        <v>-208</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-115</v>
+        <v>-208</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="14">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>86</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HDD Matrix" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="HDD Matrix" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-208</v>
+        <v>-318</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-208</v>
+        <v>-318</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-6</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="14">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>86</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.9867549668874173</v>
+        <v>1</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>0.9867549668874173</v>
+        <v>1</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.000946073793756</v>
+        <v>1.00157678965626</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-318</v>
+        <v>-158</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-318</v>
+        <v>-158</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-11</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="14">

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1</v>
+        <v>0.9933774834437086</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>1</v>
+        <v>0.9933774834437086</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.00157678965626</v>
+        <v>1.001261431725008</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-158</v>
+        <v>-294</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-158</v>
+        <v>-294</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-4</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="14">

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.9933774834437086</v>
+        <v>1</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>0.9933774834437086</v>
+        <v>1</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.001261431725008</v>
+        <v>1.00157678965626</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-294</v>
+        <v>-161</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-294</v>
+        <v>-161</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-10</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="14">

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HDD Matrix" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="HDD Matrix" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1</v>
+        <v>0.9867549668874173</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>1</v>
+        <v>0.9867549668874173</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.00157678965626</v>
+        <v>1.000946073793756</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-161</v>
+        <v>-280</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-161</v>
+        <v>-280</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-4</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="14">

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.9867549668874173</v>
+        <v>1</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>0.9867549668874173</v>
+        <v>1</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.000946073793756</v>
+        <v>1.00157678965626</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-280</v>
+        <v>-156</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-280</v>
+        <v>-156</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-10</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="14">

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1</v>
+        <v>0.9867549668874173</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>1</v>
+        <v>0.9867549668874173</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.00157678965626</v>
+        <v>1.000946073793756</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-156</v>
+        <v>-274</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-156</v>
+        <v>-274</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-4</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="14">

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.9867549668874173</v>
+        <v>1</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>0.9867549668874173</v>
+        <v>1</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.000946073793756</v>
+        <v>1.00157678965626</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-274</v>
+        <v>-150</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-274</v>
+        <v>-150</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-9</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="14">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>86</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1</v>
+        <v>0.9801324503311258</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>1</v>
+        <v>0.9801324503311258</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.00157678965626</v>
+        <v>1.000630715862504</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-150</v>
+        <v>-302</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-150</v>
+        <v>-302</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-3</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="14">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>86</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.9801324503311258</v>
+        <v>1</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>0.9801324503311258</v>
+        <v>1</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.000630715862504</v>
+        <v>1.00157678965626</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-302</v>
+        <v>-147</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-302</v>
+        <v>-147</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-11</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="14">

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1</v>
+        <v>0.9867549668874173</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>1</v>
+        <v>0.9867549668874173</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.00157678965626</v>
+        <v>1.000946073793756</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-147</v>
+        <v>-303</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-147</v>
+        <v>-303</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-3</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="14">

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.9867549668874173</v>
+        <v>1</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>0.9867549668874173</v>
+        <v>1</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.000946073793756</v>
+        <v>1.00157678965626</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-303</v>
+        <v>-137</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-303</v>
+        <v>-137</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-11</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="14">

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1</v>
+        <v>0.9933774834437086</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>1</v>
+        <v>0.9933774834437086</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.00157678965626</v>
+        <v>1.001261431725008</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-137</v>
+        <v>-301</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-137</v>
+        <v>-301</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-3</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="14">

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.9933774834437086</v>
+        <v>1</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>0.9933774834437086</v>
+        <v>1</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.001261431725008</v>
+        <v>1.00157678965626</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-301</v>
+        <v>-157</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-301</v>
+        <v>-157</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-11</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="14">

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1</v>
+        <v>0.9933774834437086</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>1</v>
+        <v>0.9933774834437086</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.00157678965626</v>
+        <v>1.001261431725008</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-157</v>
+        <v>-290</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-157</v>
+        <v>-290</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-4</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="14">

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.9933774834437086</v>
+        <v>1</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>0.9933774834437086</v>
+        <v>1</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.001261431725008</v>
+        <v>1.00157678965626</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-290</v>
+        <v>-156</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-290</v>
+        <v>-156</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-10</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="14">

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1</v>
+        <v>0.9801324503311258</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>1</v>
+        <v>0.9801324503311258</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.00157678965626</v>
+        <v>1.000630715862504</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-156</v>
+        <v>-287</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-156</v>
+        <v>-287</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-4</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="14">

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.9801324503311258</v>
+        <v>1</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>0.9801324503311258</v>
+        <v>1</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.000630715862504</v>
+        <v>1.00157678965626</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-287</v>
+        <v>-129</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-287</v>
+        <v>-129</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-10</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="14">

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1</v>
+        <v>0.9735099337748344</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>1</v>
+        <v>0.9735099337748344</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.00157678965626</v>
+        <v>1.000315357931252</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-129</v>
+        <v>-301</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-129</v>
+        <v>-301</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-2</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="14">

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.9735099337748344</v>
+        <v>1</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>0.9735099337748344</v>
+        <v>1</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.000315357931252</v>
+        <v>1.00157678965626</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-301</v>
+        <v>-153</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-301</v>
+        <v>-153</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-11</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="14">

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1</v>
+        <v>0.9602649006622517</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>1</v>
+        <v>0.9602649006622517</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.00157678965626</v>
+        <v>0.9996846420687481</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-153</v>
+        <v>-293</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-153</v>
+        <v>-293</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-4</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="14">

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.9602649006622517</v>
+        <v>1</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>0.9602649006622517</v>
+        <v>1</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>0.9996846420687481</v>
+        <v>1.00157678965626</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-293</v>
+        <v>-111</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-293</v>
+        <v>-115</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-10</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="14">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>86</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1</v>
+        <v>0.9735099337748344</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>1</v>
+        <v>0.9735099337748344</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.00157678965626</v>
+        <v>1.000315357931252</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-111</v>
+        <v>-283</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-115</v>
+        <v>-283</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-2</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="14">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>86</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.9735099337748344</v>
+        <v>1</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>0.9735099337748344</v>
+        <v>1</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.000315357931252</v>
+        <v>1.00157678965626</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-283</v>
+        <v>-108</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-283</v>
+        <v>-115</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-10</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="14">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>86</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1</v>
+        <v>0.9668874172185431</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>1</v>
+        <v>0.9668874172185431</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.00157678965626</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-108</v>
+        <v>-271</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-115</v>
+        <v>-271</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-1</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="14">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>86</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.9668874172185431</v>
+        <v>1</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>0.9668874172185431</v>
+        <v>1</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1</v>
+        <v>1.00157678965626</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-271</v>
+        <v>61</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-271</v>
+        <v>-115</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>86</v>
@@ -1364,7 +1364,7 @@
         <v>77</v>
       </c>
       <c r="Z14" s="5" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1</v>
+        <v>0.9933774834437086</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>1</v>
+        <v>0.9933774834437086</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.00157678965626</v>
+        <v>1.001261431725008</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>61</v>
+        <v>-137</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-115</v>
+        <v>-137</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>7</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="14">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>86</v>
@@ -1364,7 +1364,7 @@
         <v>77</v>
       </c>
       <c r="Z14" s="5" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.9933774834437086</v>
+        <v>1</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>0.9933774834437086</v>
+        <v>1</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.001261431725008</v>
+        <v>1.00157678965626</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-137</v>
+        <v>44</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>52</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-137</v>
+        <v>-115</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>86</v>
@@ -1364,7 +1364,7 @@
         <v>77</v>
       </c>
       <c r="Z14" s="5" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1</v>
+        <v>0.9933774834437086</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>1</v>
+        <v>0.9933774834437086</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.00157678965626</v>
+        <v>1.001261431725008</v>
       </c>
     </row>
     <row r="13">
@@ -1210,79 +1210,79 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>44</v>
+        <v>-98</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>-30</v>
+        <v>-26</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>-115</v>
+        <v>-112</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>-26</v>
+        <v>-25</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="J13" s="10" t="n">
         <v>-42</v>
       </c>
       <c r="K13" s="10" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L13" s="10" t="n">
-        <v>-16</v>
+        <v>-14</v>
       </c>
       <c r="M13" s="10" t="n">
-        <v>-34</v>
+        <v>-40</v>
       </c>
       <c r="N13" s="10" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="O13" s="10" t="n">
-        <v>-26</v>
+        <v>-18</v>
       </c>
       <c r="P13" s="10" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Q13" s="10" t="n">
-        <v>-78</v>
+        <v>-77</v>
       </c>
       <c r="R13" s="10" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="S13" s="10" t="n">
-        <v>-44</v>
+        <v>-51</v>
       </c>
       <c r="T13" s="10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="U13" s="10" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="V13" s="10" t="n">
-        <v>-24</v>
+        <v>-21</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-115</v>
+        <v>-112</v>
       </c>
       <c r="X13" s="10" t="n">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="Y13" s="11" t="n">
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="14">
@@ -1292,46 +1292,46 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>86</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>63</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H14" s="5" t="n">
         <v>75</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J14" s="5" t="n">
         <v>72</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L14" s="5" t="n">
         <v>79</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N14" s="5" t="n">
         <v>83</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P14" s="5" t="n">
         <v>83</v>
@@ -1343,7 +1343,7 @@
         <v>76</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T14" s="5" t="n">
         <v>73</v>
@@ -1364,7 +1364,7 @@
         <v>77</v>
       </c>
       <c r="Z14" s="5" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.9933774834437086</v>
+        <v>1</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>0.9933774834437086</v>
+        <v>1</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.001261431725008</v>
+        <v>1.00157678965626</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-98</v>
+        <v>37</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>55</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>86</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1</v>
+        <v>0.9933774834437086</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>1</v>
+        <v>0.9933774834437086</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.00157678965626</v>
+        <v>1.001261431725008</v>
       </c>
     </row>
     <row r="13">
@@ -1210,79 +1210,79 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
+        <v>-139</v>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>57</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>-29</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>-108</v>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>-22</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>-14</v>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>82</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>-47</v>
+      </c>
+      <c r="K13" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="C13" s="10" t="n">
-        <v>55</v>
-      </c>
-      <c r="D13" s="10" t="n">
-        <v>-26</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>101</v>
-      </c>
-      <c r="F13" s="10" t="n">
-        <v>-112</v>
-      </c>
-      <c r="G13" s="10" t="n">
-        <v>-25</v>
-      </c>
-      <c r="H13" s="10" t="n">
-        <v>-17</v>
-      </c>
-      <c r="I13" s="10" t="n">
-        <v>83</v>
-      </c>
-      <c r="J13" s="10" t="n">
-        <v>-42</v>
-      </c>
-      <c r="K13" s="10" t="n">
-        <v>35</v>
-      </c>
       <c r="L13" s="10" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="M13" s="10" t="n">
-        <v>-40</v>
+        <v>-36</v>
       </c>
       <c r="N13" s="10" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="O13" s="10" t="n">
         <v>-18</v>
       </c>
       <c r="P13" s="10" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="Q13" s="10" t="n">
-        <v>-77</v>
+        <v>-79</v>
       </c>
       <c r="R13" s="10" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S13" s="10" t="n">
-        <v>-51</v>
+        <v>-52</v>
       </c>
       <c r="T13" s="10" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="U13" s="10" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="V13" s="10" t="n">
-        <v>-21</v>
+        <v>-27</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-112</v>
+        <v>-139</v>
       </c>
       <c r="X13" s="10" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Y13" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>6</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="14">
@@ -1292,13 +1292,13 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>86</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>82</v>
@@ -1307,7 +1307,7 @@
         <v>63</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H14" s="5" t="n">
         <v>75</v>
@@ -1316,25 +1316,25 @@
         <v>85</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K14" s="5" t="n">
         <v>78</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M14" s="5" t="n">
         <v>70</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O14" s="5" t="n">
         <v>74</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>70</v>
@@ -1343,16 +1343,16 @@
         <v>76</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="T14" s="5" t="n">
         <v>73</v>
       </c>
       <c r="U14" s="5" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="V14" s="5" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="W14" s="5" t="n">
         <v>63</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.9933774834437086</v>
+        <v>1</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>0.9933774834437086</v>
+        <v>1</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.001261431725008</v>
+        <v>1.00157678965626</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-139</v>
+        <v>13</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>57</v>
@@ -1273,7 +1273,7 @@
         <v>-27</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-139</v>
+        <v>-108</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>100</v>
@@ -1282,7 +1282,7 @@
         <v>5</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>86</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1</v>
+        <v>0.9867549668874173</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>1</v>
+        <v>0.9867549668874173</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.00157678965626</v>
+        <v>1.000946073793756</v>
       </c>
     </row>
     <row r="13">
@@ -1210,79 +1210,79 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>13</v>
+        <v>-155</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>-29</v>
+        <v>-30</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>-108</v>
+        <v>-102</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>-14</v>
+        <v>-9</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>-47</v>
+        <v>-53</v>
       </c>
       <c r="K13" s="10" t="n">
         <v>37</v>
       </c>
       <c r="L13" s="10" t="n">
-        <v>-12</v>
+        <v>-17</v>
       </c>
       <c r="M13" s="10" t="n">
-        <v>-36</v>
+        <v>-31</v>
       </c>
       <c r="N13" s="10" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="O13" s="10" t="n">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="P13" s="10" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q13" s="10" t="n">
-        <v>-79</v>
+        <v>-82</v>
       </c>
       <c r="R13" s="10" t="n">
         <v>64</v>
       </c>
       <c r="S13" s="10" t="n">
-        <v>-52</v>
+        <v>-57</v>
       </c>
       <c r="T13" s="10" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="U13" s="10" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="V13" s="10" t="n">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-108</v>
+        <v>-155</v>
       </c>
       <c r="X13" s="10" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="Y13" s="11" t="n">
         <v>5</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="14">
@@ -1292,31 +1292,31 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>76</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>63</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I14" s="5" t="n">
         <v>85</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K14" s="5" t="n">
         <v>78</v>
@@ -1325,7 +1325,7 @@
         <v>80</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="N14" s="5" t="n">
         <v>82</v>
@@ -1337,7 +1337,7 @@
         <v>84</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R14" s="5" t="n">
         <v>76</v>
@@ -1346,10 +1346,10 @@
         <v>70</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="U14" s="5" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="V14" s="5" t="n">
         <v>72</v>
@@ -1358,7 +1358,7 @@
         <v>63</v>
       </c>
       <c r="X14" s="5" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Y14" s="12" t="n">
         <v>77</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.9867549668874173</v>
+        <v>1</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>0.9867549668874173</v>
+        <v>1</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.000946073793756</v>
+        <v>1.00157678965626</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-155</v>
+        <v>13</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>56</v>
@@ -1273,7 +1273,7 @@
         <v>-28</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-155</v>
+        <v>-102</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>106</v>
@@ -1282,7 +1282,7 @@
         <v>5</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>85</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1</v>
+        <v>0.9933774834437086</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>1</v>
+        <v>0.9933774834437086</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.00157678965626</v>
+        <v>1.001261431725008</v>
       </c>
     </row>
     <row r="13">
@@ -1210,79 +1210,79 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>13</v>
+        <v>-126</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>-30</v>
+        <v>-28</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>-102</v>
+        <v>-100</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>-23</v>
+        <v>-22</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>-9</v>
+        <v>-14</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>-53</v>
+        <v>-51</v>
       </c>
       <c r="K13" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="L13" s="10" t="n">
+        <v>-22</v>
+      </c>
+      <c r="M13" s="10" t="n">
+        <v>-34</v>
+      </c>
+      <c r="N13" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="L13" s="10" t="n">
+      <c r="O13" s="10" t="n">
         <v>-17</v>
       </c>
-      <c r="M13" s="10" t="n">
-        <v>-31</v>
-      </c>
-      <c r="N13" s="10" t="n">
-        <v>32</v>
-      </c>
-      <c r="O13" s="10" t="n">
-        <v>-19</v>
-      </c>
       <c r="P13" s="10" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="Q13" s="10" t="n">
-        <v>-82</v>
+        <v>-84</v>
       </c>
       <c r="R13" s="10" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="S13" s="10" t="n">
         <v>-57</v>
       </c>
       <c r="T13" s="10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="U13" s="10" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="V13" s="10" t="n">
-        <v>-28</v>
+        <v>-25</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-102</v>
+        <v>-126</v>
       </c>
       <c r="X13" s="10" t="n">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="Y13" s="11" t="n">
         <v>5</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="14">
@@ -1292,28 +1292,28 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>76</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G14" s="5" t="n">
         <v>76</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J14" s="5" t="n">
         <v>70</v>
@@ -1322,13 +1322,13 @@
         <v>78</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M14" s="5" t="n">
         <v>71</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O14" s="5" t="n">
         <v>74</v>
@@ -1337,7 +1337,7 @@
         <v>84</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="R14" s="5" t="n">
         <v>76</v>
@@ -1352,13 +1352,13 @@
         <v>85</v>
       </c>
       <c r="V14" s="5" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="W14" s="5" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="X14" s="5" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Y14" s="12" t="n">
         <v>77</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.9933774834437086</v>
+        <v>1</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>0.9933774834437086</v>
+        <v>1</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.001261431725008</v>
+        <v>1.00157678965626</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-126</v>
+        <v>-21</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>57</v>
@@ -1273,7 +1273,7 @@
         <v>-25</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-126</v>
+        <v>-100</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>99</v>
@@ -1282,7 +1282,7 @@
         <v>5</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>86</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -1210,79 +1210,79 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-21</v>
+        <v>-142</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>-28</v>
+        <v>-26</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F13" s="10" t="n">
         <v>-100</v>
       </c>
       <c r="G13" s="10" t="n">
+        <v>-23</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>-17</v>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>101</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>-56</v>
+      </c>
+      <c r="K13" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="L13" s="10" t="n">
+        <v>-24</v>
+      </c>
+      <c r="M13" s="10" t="n">
+        <v>-36</v>
+      </c>
+      <c r="N13" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="O13" s="10" t="n">
         <v>-22</v>
       </c>
-      <c r="H13" s="10" t="n">
-        <v>-14</v>
-      </c>
-      <c r="I13" s="10" t="n">
-        <v>95</v>
-      </c>
-      <c r="J13" s="10" t="n">
-        <v>-51</v>
-      </c>
-      <c r="K13" s="10" t="n">
-        <v>38</v>
-      </c>
-      <c r="L13" s="10" t="n">
-        <v>-22</v>
-      </c>
-      <c r="M13" s="10" t="n">
-        <v>-34</v>
-      </c>
-      <c r="N13" s="10" t="n">
-        <v>37</v>
-      </c>
-      <c r="O13" s="10" t="n">
-        <v>-17</v>
-      </c>
       <c r="P13" s="10" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Q13" s="10" t="n">
-        <v>-84</v>
+        <v>-78</v>
       </c>
       <c r="R13" s="10" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="S13" s="10" t="n">
-        <v>-57</v>
+        <v>-54</v>
       </c>
       <c r="T13" s="10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="U13" s="10" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="V13" s="10" t="n">
         <v>-25</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-100</v>
+        <v>-142</v>
       </c>
       <c r="X13" s="10" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="Y13" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="14">
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>76</v>
@@ -1313,31 +1313,31 @@
         <v>75</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K14" s="5" t="n">
+        <v>79</v>
+      </c>
+      <c r="L14" s="5" t="n">
         <v>78</v>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v>79</v>
       </c>
       <c r="M14" s="5" t="n">
         <v>71</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P14" s="5" t="n">
         <v>84</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="R14" s="5" t="n">
         <v>76</v>
@@ -1349,7 +1349,7 @@
         <v>74</v>
       </c>
       <c r="U14" s="5" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V14" s="5" t="n">
         <v>73</v>
@@ -1358,7 +1358,7 @@
         <v>64</v>
       </c>
       <c r="X14" s="5" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Y14" s="12" t="n">
         <v>77</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-142</v>
+        <v>-17</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>46</v>
@@ -1273,7 +1273,7 @@
         <v>-25</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-142</v>
+        <v>-100</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>101</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>85</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1</v>
+        <v>0.9933774834437086</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>1</v>
+        <v>0.9933774834437086</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.00157678965626</v>
+        <v>1.001261431725008</v>
       </c>
     </row>
     <row r="13">
@@ -1210,79 +1210,79 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-17</v>
+        <v>-113</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D13" s="10" t="n">
         <v>-26</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F13" s="10" t="n">
         <v>-100</v>
       </c>
       <c r="G13" s="10" t="n">
+        <v>-29</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>94</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>-48</v>
+      </c>
+      <c r="K13" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="L13" s="10" t="n">
+        <v>-22</v>
+      </c>
+      <c r="M13" s="10" t="n">
+        <v>-38</v>
+      </c>
+      <c r="N13" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="O13" s="10" t="n">
         <v>-23</v>
       </c>
-      <c r="H13" s="10" t="n">
-        <v>-17</v>
-      </c>
-      <c r="I13" s="10" t="n">
-        <v>101</v>
-      </c>
-      <c r="J13" s="10" t="n">
-        <v>-56</v>
-      </c>
-      <c r="K13" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="L13" s="10" t="n">
-        <v>-24</v>
-      </c>
-      <c r="M13" s="10" t="n">
-        <v>-36</v>
-      </c>
-      <c r="N13" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="O13" s="10" t="n">
-        <v>-22</v>
-      </c>
       <c r="P13" s="10" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="Q13" s="10" t="n">
         <v>-78</v>
       </c>
       <c r="R13" s="10" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="S13" s="10" t="n">
-        <v>-54</v>
+        <v>-58</v>
       </c>
       <c r="T13" s="10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="U13" s="10" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="V13" s="10" t="n">
-        <v>-25</v>
+        <v>-27</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-100</v>
+        <v>-113</v>
       </c>
       <c r="X13" s="10" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Y13" s="11" t="n">
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="14">
@@ -1292,34 +1292,34 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>76</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>64</v>
       </c>
       <c r="G14" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="H14" s="5" t="n">
         <v>76</v>
       </c>
-      <c r="H14" s="5" t="n">
-        <v>75</v>
-      </c>
       <c r="I14" s="5" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L14" s="5" t="n">
         <v>78</v>
@@ -1328,19 +1328,19 @@
         <v>71</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O14" s="5" t="n">
         <v>73</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>69</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S14" s="5" t="n">
         <v>70</v>
@@ -1352,13 +1352,13 @@
         <v>84</v>
       </c>
       <c r="V14" s="5" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="W14" s="5" t="n">
         <v>64</v>
       </c>
       <c r="X14" s="5" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Y14" s="12" t="n">
         <v>77</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.9933774834437086</v>
+        <v>1</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>0.9933774834437086</v>
+        <v>1</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.001261431725008</v>
+        <v>1.00157678965626</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-113</v>
+        <v>-16</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>42</v>
@@ -1273,7 +1273,7 @@
         <v>-27</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-113</v>
+        <v>-100</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>102</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>84</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1</v>
+        <v>0.9933774834437086</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>1</v>
+        <v>0.9933774834437086</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.00157678965626</v>
+        <v>1.001261431725008</v>
       </c>
     </row>
     <row r="13">
@@ -1210,79 +1210,79 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-16</v>
+        <v>-102</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>-26</v>
+        <v>-24</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>-100</v>
+        <v>-101</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>-29</v>
+        <v>-27</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>-11</v>
+        <v>-17</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>-48</v>
+        <v>-47</v>
       </c>
       <c r="K13" s="10" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="L13" s="10" t="n">
-        <v>-22</v>
+        <v>-21</v>
       </c>
       <c r="M13" s="10" t="n">
-        <v>-38</v>
+        <v>-36</v>
       </c>
       <c r="N13" s="10" t="n">
         <v>46</v>
       </c>
       <c r="O13" s="10" t="n">
-        <v>-23</v>
+        <v>-21</v>
       </c>
       <c r="P13" s="10" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Q13" s="10" t="n">
-        <v>-78</v>
+        <v>-77</v>
       </c>
       <c r="R13" s="10" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="S13" s="10" t="n">
-        <v>-58</v>
+        <v>-64</v>
       </c>
       <c r="T13" s="10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="U13" s="10" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="V13" s="10" t="n">
-        <v>-27</v>
+        <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-100</v>
+        <v>-102</v>
       </c>
       <c r="X13" s="10" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="Y13" s="11" t="n">
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="14">
@@ -1292,40 +1292,40 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>76</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>64</v>
       </c>
       <c r="G14" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="H14" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="H14" s="5" t="n">
-        <v>76</v>
-      </c>
       <c r="I14" s="5" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J14" s="5" t="n">
         <v>70</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L14" s="5" t="n">
         <v>78</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N14" s="5" t="n">
         <v>85</v>
@@ -1334,16 +1334,16 @@
         <v>73</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R14" s="5" t="n">
         <v>77</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="T14" s="5" t="n">
         <v>74</v>
@@ -1352,13 +1352,13 @@
         <v>84</v>
       </c>
       <c r="V14" s="5" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="W14" s="5" t="n">
         <v>64</v>
       </c>
       <c r="X14" s="5" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Y14" s="12" t="n">
         <v>77</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.9933774834437086</v>
+        <v>1</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>0.9933774834437086</v>
+        <v>1</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.001261431725008</v>
+        <v>1.00157678965626</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-102</v>
+        <v>0</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>50</v>
@@ -1273,7 +1273,7 @@
         <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-102</v>
+        <v>-101</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>97</v>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>85</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1</v>
+        <v>0.9933774834437086</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>1</v>
+        <v>0.9933774834437086</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.00157678965626</v>
+        <v>1.001261431725008</v>
       </c>
     </row>
     <row r="13">
@@ -1210,79 +1210,79 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>0</v>
+        <v>-86</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>-24</v>
+        <v>-17</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>-101</v>
+        <v>-100</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>-27</v>
+        <v>-34</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>-17</v>
+        <v>-6</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>-47</v>
+        <v>-42</v>
       </c>
       <c r="K13" s="10" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L13" s="10" t="n">
-        <v>-21</v>
+        <v>-15</v>
       </c>
       <c r="M13" s="10" t="n">
-        <v>-36</v>
+        <v>-38</v>
       </c>
       <c r="N13" s="10" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O13" s="10" t="n">
         <v>-21</v>
       </c>
       <c r="P13" s="10" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="Q13" s="10" t="n">
-        <v>-77</v>
+        <v>-84</v>
       </c>
       <c r="R13" s="10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S13" s="10" t="n">
-        <v>-64</v>
+        <v>-62</v>
       </c>
       <c r="T13" s="10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="U13" s="10" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="V13" s="10" t="n">
-        <v>-24</v>
+        <v>-31</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-101</v>
+        <v>-100</v>
       </c>
       <c r="X13" s="10" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="Y13" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="14">
@@ -1292,13 +1292,13 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>85</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>82</v>
@@ -1307,13 +1307,13 @@
         <v>64</v>
       </c>
       <c r="G14" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="H14" s="5" t="n">
         <v>76</v>
       </c>
-      <c r="H14" s="5" t="n">
-        <v>75</v>
-      </c>
       <c r="I14" s="5" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J14" s="5" t="n">
         <v>70</v>
@@ -1322,22 +1322,22 @@
         <v>77</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M14" s="5" t="n">
         <v>72</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O14" s="5" t="n">
         <v>73</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R14" s="5" t="n">
         <v>77</v>
@@ -1346,19 +1346,19 @@
         <v>69</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U14" s="5" t="n">
         <v>84</v>
       </c>
       <c r="V14" s="5" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="W14" s="5" t="n">
         <v>64</v>
       </c>
       <c r="X14" s="5" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Y14" s="12" t="n">
         <v>77</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.9933774834437086</v>
+        <v>1</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>0.9933774834437086</v>
+        <v>1</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.001261431725008</v>
+        <v>1.00157678965626</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-86</v>
+        <v>-8</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>49</v>
@@ -1282,7 +1282,7 @@
         <v>5</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>85</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1</v>
+        <v>0.9867549668874173</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>1</v>
+        <v>0.9867549668874173</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.00157678965626</v>
+        <v>1.000946073793756</v>
       </c>
     </row>
     <row r="13">
@@ -1210,79 +1210,79 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-8</v>
+        <v>-90</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>-17</v>
+        <v>-7</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>-100</v>
+        <v>-92</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>-34</v>
+        <v>-41</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>-42</v>
+        <v>-37</v>
       </c>
       <c r="K13" s="10" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="L13" s="10" t="n">
-        <v>-15</v>
+        <v>-13</v>
       </c>
       <c r="M13" s="10" t="n">
-        <v>-38</v>
+        <v>-41</v>
       </c>
       <c r="N13" s="10" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O13" s="10" t="n">
-        <v>-21</v>
+        <v>-16</v>
       </c>
       <c r="P13" s="10" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q13" s="10" t="n">
+        <v>-80</v>
+      </c>
+      <c r="R13" s="10" t="n">
         <v>55</v>
-      </c>
-      <c r="Q13" s="10" t="n">
-        <v>-84</v>
-      </c>
-      <c r="R13" s="10" t="n">
-        <v>63</v>
       </c>
       <c r="S13" s="10" t="n">
         <v>-62</v>
       </c>
       <c r="T13" s="10" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="U13" s="10" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="V13" s="10" t="n">
-        <v>-31</v>
+        <v>-27</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-100</v>
+        <v>-92</v>
       </c>
       <c r="X13" s="10" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="Y13" s="11" t="n">
         <v>5</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1292,43 +1292,43 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>85</v>
       </c>
       <c r="D14" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="H14" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="E14" s="5" t="n">
-        <v>82</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="H14" s="5" t="n">
+      <c r="I14" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="K14" s="5" t="n">
         <v>76</v>
       </c>
-      <c r="I14" s="5" t="n">
-        <v>86</v>
-      </c>
-      <c r="J14" s="5" t="n">
-        <v>70</v>
-      </c>
-      <c r="K14" s="5" t="n">
-        <v>77</v>
-      </c>
       <c r="L14" s="5" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O14" s="5" t="n">
         <v>73</v>
@@ -1337,7 +1337,7 @@
         <v>83</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="R14" s="5" t="n">
         <v>77</v>
@@ -1346,19 +1346,19 @@
         <v>69</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U14" s="5" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V14" s="5" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="W14" s="5" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="X14" s="5" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Y14" s="12" t="n">
         <v>77</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.9867549668874173</v>
+        <v>1</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>0.9867549668874173</v>
+        <v>1</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.000946073793756</v>
+        <v>1.00157678965626</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-90</v>
+        <v>-18</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>47</v>
@@ -1282,7 +1282,7 @@
         <v>5</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>85</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1</v>
+        <v>0.9801324503311258</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>1</v>
+        <v>0.9801324503311258</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.00157678965626</v>
+        <v>1.000630715862504</v>
       </c>
     </row>
     <row r="13">
@@ -1210,79 +1210,79 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-18</v>
+        <v>-88</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>-92</v>
+        <v>-88</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>-41</v>
+        <v>-45</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="J13" s="10" t="n">
         <v>-37</v>
       </c>
       <c r="K13" s="10" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L13" s="10" t="n">
-        <v>-13</v>
+        <v>-17</v>
       </c>
       <c r="M13" s="10" t="n">
-        <v>-41</v>
+        <v>-42</v>
       </c>
       <c r="N13" s="10" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="O13" s="10" t="n">
-        <v>-16</v>
+        <v>-23</v>
       </c>
       <c r="P13" s="10" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="Q13" s="10" t="n">
-        <v>-80</v>
+        <v>-83</v>
       </c>
       <c r="R13" s="10" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="S13" s="10" t="n">
-        <v>-62</v>
+        <v>-64</v>
       </c>
       <c r="T13" s="10" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="U13" s="10" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="V13" s="10" t="n">
-        <v>-27</v>
+        <v>-24</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-92</v>
+        <v>-88</v>
       </c>
       <c r="X13" s="10" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="Y13" s="11" t="n">
         <v>5</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1292,28 +1292,28 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>78</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J14" s="5" t="n">
         <v>71</v>
@@ -1328,16 +1328,16 @@
         <v>71</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="R14" s="5" t="n">
         <v>77</v>
@@ -1346,19 +1346,19 @@
         <v>69</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U14" s="5" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V14" s="5" t="n">
         <v>73</v>
       </c>
       <c r="W14" s="5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="X14" s="5" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Y14" s="12" t="n">
         <v>77</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.9801324503311258</v>
+        <v>1</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>0.9801324503311258</v>
+        <v>1</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.000630715862504</v>
+        <v>1.00157678965626</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-88</v>
+        <v>-23</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>48</v>
@@ -1282,7 +1282,7 @@
         <v>5</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>86</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1</v>
+        <v>0.9933774834437086</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>1</v>
+        <v>0.9933774834437086</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.00157678965626</v>
+        <v>1.001261431725008</v>
       </c>
     </row>
     <row r="13">
@@ -1210,79 +1210,79 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-23</v>
+        <v>-72</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>-88</v>
+        <v>-87</v>
       </c>
       <c r="G13" s="10" t="n">
+        <v>-49</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>82</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>-32</v>
+      </c>
+      <c r="K13" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="L13" s="10" t="n">
+        <v>-19</v>
+      </c>
+      <c r="M13" s="10" t="n">
         <v>-45</v>
-      </c>
-      <c r="H13" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="I13" s="10" t="n">
-        <v>83</v>
-      </c>
-      <c r="J13" s="10" t="n">
-        <v>-37</v>
-      </c>
-      <c r="K13" s="10" t="n">
-        <v>22</v>
-      </c>
-      <c r="L13" s="10" t="n">
-        <v>-17</v>
-      </c>
-      <c r="M13" s="10" t="n">
-        <v>-42</v>
       </c>
       <c r="N13" s="10" t="n">
         <v>54</v>
       </c>
       <c r="O13" s="10" t="n">
-        <v>-23</v>
+        <v>-25</v>
       </c>
       <c r="P13" s="10" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="Q13" s="10" t="n">
-        <v>-83</v>
+        <v>-82</v>
       </c>
       <c r="R13" s="10" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="S13" s="10" t="n">
-        <v>-64</v>
+        <v>-61</v>
       </c>
       <c r="T13" s="10" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="U13" s="10" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="V13" s="10" t="n">
-        <v>-24</v>
+        <v>-22</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-88</v>
+        <v>-87</v>
       </c>
       <c r="X13" s="10" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y13" s="11" t="n">
         <v>5</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1292,13 +1292,13 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>80</v>
@@ -1310,19 +1310,19 @@
         <v>73</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K14" s="5" t="n">
         <v>76</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M14" s="5" t="n">
         <v>71</v>
@@ -1337,19 +1337,19 @@
         <v>84</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U14" s="5" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V14" s="5" t="n">
         <v>73</v>
@@ -1358,7 +1358,7 @@
         <v>66</v>
       </c>
       <c r="X14" s="5" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Y14" s="12" t="n">
         <v>77</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.9933774834437086</v>
+        <v>1</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>0.9933774834437086</v>
+        <v>1</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.001261431725008</v>
+        <v>1.00157678965626</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-72</v>
+        <v>-18</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>53</v>
@@ -1282,7 +1282,7 @@
         <v>5</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>87</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1</v>
+        <v>0.9933774834437086</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>1</v>
+        <v>0.9933774834437086</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.00157678965626</v>
+        <v>1.001261431725008</v>
       </c>
     </row>
     <row r="13">
@@ -1210,79 +1210,79 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-18</v>
+        <v>-58</v>
       </c>
       <c r="C13" s="10" t="n">
+        <v>51</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>-7</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>79</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>-80</v>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>-59</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>79</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>-29</v>
+      </c>
+      <c r="K13" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="L13" s="10" t="n">
+        <v>-16</v>
+      </c>
+      <c r="M13" s="10" t="n">
+        <v>-43</v>
+      </c>
+      <c r="N13" s="10" t="n">
         <v>53</v>
       </c>
-      <c r="D13" s="10" t="n">
-        <v>-5</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>77</v>
-      </c>
-      <c r="F13" s="10" t="n">
-        <v>-87</v>
-      </c>
-      <c r="G13" s="10" t="n">
-        <v>-49</v>
-      </c>
-      <c r="H13" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="I13" s="10" t="n">
-        <v>82</v>
-      </c>
-      <c r="J13" s="10" t="n">
-        <v>-32</v>
-      </c>
-      <c r="K13" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="L13" s="10" t="n">
-        <v>-19</v>
-      </c>
-      <c r="M13" s="10" t="n">
-        <v>-45</v>
-      </c>
-      <c r="N13" s="10" t="n">
-        <v>54</v>
-      </c>
       <c r="O13" s="10" t="n">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="P13" s="10" t="n">
         <v>58</v>
       </c>
       <c r="Q13" s="10" t="n">
-        <v>-82</v>
+        <v>-76</v>
       </c>
       <c r="R13" s="10" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="S13" s="10" t="n">
-        <v>-61</v>
+        <v>-56</v>
       </c>
       <c r="T13" s="10" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="U13" s="10" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="V13" s="10" t="n">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-87</v>
+        <v>-80</v>
       </c>
       <c r="X13" s="10" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="Y13" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>77</v>
@@ -1304,13 +1304,13 @@
         <v>80</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I14" s="5" t="n">
         <v>83</v>
@@ -1322,31 +1322,31 @@
         <v>76</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O14" s="5" t="n">
         <v>72</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>68</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="U14" s="5" t="n">
         <v>83</v>
@@ -1355,10 +1355,10 @@
         <v>73</v>
       </c>
       <c r="W14" s="5" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="X14" s="5" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Y14" s="12" t="n">
         <v>77</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.9933774834437086</v>
+        <v>1</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>0.9933774834437086</v>
+        <v>1</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.001261431725008</v>
+        <v>1.00157678965626</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-58</v>
+        <v>-20</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>51</v>
@@ -1282,7 +1282,7 @@
         <v>6</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>86</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1</v>
+        <v>0.9933774834437086</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>1</v>
+        <v>0.9933774834437086</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.00157678965626</v>
+        <v>1.001261431725008</v>
       </c>
     </row>
     <row r="13">
@@ -1210,79 +1210,79 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-20</v>
+        <v>-59</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F13" s="10" t="n">
+        <v>-76</v>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>-61</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>81</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>-32</v>
+      </c>
+      <c r="K13" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="L13" s="10" t="n">
+        <v>-14</v>
+      </c>
+      <c r="M13" s="10" t="n">
+        <v>-40</v>
+      </c>
+      <c r="N13" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="O13" s="10" t="n">
+        <v>-23</v>
+      </c>
+      <c r="P13" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q13" s="10" t="n">
         <v>-80</v>
       </c>
-      <c r="G13" s="10" t="n">
-        <v>-59</v>
-      </c>
-      <c r="H13" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="I13" s="10" t="n">
-        <v>79</v>
-      </c>
-      <c r="J13" s="10" t="n">
-        <v>-29</v>
-      </c>
-      <c r="K13" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="L13" s="10" t="n">
-        <v>-16</v>
-      </c>
-      <c r="M13" s="10" t="n">
-        <v>-43</v>
-      </c>
-      <c r="N13" s="10" t="n">
-        <v>53</v>
-      </c>
-      <c r="O13" s="10" t="n">
+      <c r="R13" s="10" t="n">
+        <v>52</v>
+      </c>
+      <c r="S13" s="10" t="n">
+        <v>-48</v>
+      </c>
+      <c r="T13" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="U13" s="10" t="n">
+        <v>66</v>
+      </c>
+      <c r="V13" s="10" t="n">
         <v>-26</v>
-      </c>
-      <c r="P13" s="10" t="n">
-        <v>58</v>
-      </c>
-      <c r="Q13" s="10" t="n">
-        <v>-76</v>
-      </c>
-      <c r="R13" s="10" t="n">
-        <v>53</v>
-      </c>
-      <c r="S13" s="10" t="n">
-        <v>-56</v>
-      </c>
-      <c r="T13" s="10" t="n">
-        <v>22</v>
-      </c>
-      <c r="U13" s="10" t="n">
-        <v>72</v>
-      </c>
-      <c r="V13" s="10" t="n">
-        <v>-23</v>
       </c>
       <c r="W13" s="10" t="n">
         <v>-80</v>
       </c>
       <c r="X13" s="10" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="Y13" s="11" t="n">
         <v>6</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>86</v>
@@ -1301,25 +1301,25 @@
         <v>77</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G14" s="5" t="n">
         <v>72</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L14" s="5" t="n">
         <v>78</v>
@@ -1337,19 +1337,19 @@
         <v>85</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="R14" s="5" t="n">
         <v>75</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T14" s="5" t="n">
         <v>75</v>
       </c>
       <c r="U14" s="5" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V14" s="5" t="n">
         <v>73</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.9933774834437086</v>
+        <v>1</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>0.9933774834437086</v>
+        <v>1</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.001261431725008</v>
+        <v>1.00157678965626</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-59</v>
+        <v>-34</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>54</v>
@@ -1282,7 +1282,7 @@
         <v>6</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>86</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1</v>
+        <v>0.9933774834437086</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>1</v>
+        <v>0.9933774834437086</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.00157678965626</v>
+        <v>1.001261431725008</v>
       </c>
     </row>
     <row r="13">
@@ -1210,79 +1210,79 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-34</v>
+        <v>-61</v>
       </c>
       <c r="C13" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>69</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>-74</v>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>-59</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>78</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>-36</v>
+      </c>
+      <c r="K13" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="L13" s="10" t="n">
+        <v>-18</v>
+      </c>
+      <c r="M13" s="10" t="n">
+        <v>-43</v>
+      </c>
+      <c r="N13" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="O13" s="10" t="n">
+        <v>-17</v>
+      </c>
+      <c r="P13" s="10" t="n">
         <v>54</v>
       </c>
-      <c r="D13" s="10" t="n">
-        <v>-4</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>74</v>
-      </c>
-      <c r="F13" s="10" t="n">
-        <v>-76</v>
-      </c>
-      <c r="G13" s="10" t="n">
-        <v>-61</v>
-      </c>
-      <c r="H13" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="I13" s="10" t="n">
-        <v>81</v>
-      </c>
-      <c r="J13" s="10" t="n">
-        <v>-32</v>
-      </c>
-      <c r="K13" s="10" t="n">
-        <v>23</v>
-      </c>
-      <c r="L13" s="10" t="n">
-        <v>-14</v>
-      </c>
-      <c r="M13" s="10" t="n">
-        <v>-40</v>
-      </c>
-      <c r="N13" s="10" t="n">
-        <v>55</v>
-      </c>
-      <c r="O13" s="10" t="n">
-        <v>-23</v>
-      </c>
-      <c r="P13" s="10" t="n">
-        <v>56</v>
-      </c>
       <c r="Q13" s="10" t="n">
-        <v>-80</v>
+        <v>-87</v>
       </c>
       <c r="R13" s="10" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="S13" s="10" t="n">
-        <v>-48</v>
+        <v>-56</v>
       </c>
       <c r="T13" s="10" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="U13" s="10" t="n">
         <v>66</v>
       </c>
       <c r="V13" s="10" t="n">
-        <v>-26</v>
+        <v>-31</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-80</v>
+        <v>-87</v>
       </c>
       <c r="X13" s="10" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="Y13" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1292,16 +1292,16 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>86</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>68</v>
@@ -1310,52 +1310,52 @@
         <v>72</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J14" s="5" t="n">
         <v>71</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L14" s="5" t="n">
         <v>78</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="N14" s="5" t="n">
         <v>85</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P14" s="5" t="n">
         <v>85</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U14" s="5" t="n">
         <v>82</v>
       </c>
       <c r="V14" s="5" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="W14" s="5" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="X14" s="5" t="n">
         <v>86</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.9933774834437086</v>
+        <v>1</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>0.9933774834437086</v>
+        <v>1</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.001261431725008</v>
+        <v>1.00157678965626</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-61</v>
+        <v>-45</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>56</v>
@@ -1282,7 +1282,7 @@
         <v>7</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1</v>
+        <v>0.9933774834437086</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>1</v>
+        <v>0.9933774834437086</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.00157678965626</v>
+        <v>1.001261431725008</v>
       </c>
     </row>
     <row r="13">
@@ -1210,79 +1210,79 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-45</v>
+        <v>-52</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="F13" s="10" t="n">
         <v>-74</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>-59</v>
+        <v>-54</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>-36</v>
+        <v>-34</v>
       </c>
       <c r="K13" s="10" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L13" s="10" t="n">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="M13" s="10" t="n">
-        <v>-43</v>
+        <v>-51</v>
       </c>
       <c r="N13" s="10" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="O13" s="10" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="P13" s="10" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="Q13" s="10" t="n">
-        <v>-87</v>
+        <v>-96</v>
       </c>
       <c r="R13" s="10" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="S13" s="10" t="n">
-        <v>-56</v>
+        <v>-57</v>
       </c>
       <c r="T13" s="10" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="U13" s="10" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="V13" s="10" t="n">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-87</v>
+        <v>-96</v>
       </c>
       <c r="X13" s="10" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="Y13" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1307,16 +1307,16 @@
         <v>68</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I14" s="5" t="n">
         <v>83</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K14" s="5" t="n">
         <v>78</v>
@@ -1325,22 +1325,22 @@
         <v>78</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="S14" s="5" t="n">
         <v>71</v>
@@ -1349,13 +1349,13 @@
         <v>76</v>
       </c>
       <c r="U14" s="5" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="V14" s="5" t="n">
         <v>72</v>
       </c>
       <c r="W14" s="5" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="X14" s="5" t="n">
         <v>86</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -964,7 +964,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>31</v>
@@ -1027,7 +1027,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X8" s="5" t="n">
         <v>31</v>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>151</v>
@@ -1109,7 +1109,7 @@
         <v>151</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>152</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.9933774834437086</v>
+        <v>1</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>0.9933774834437086</v>
+        <v>1</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>1.006622516556291</v>
@@ -1200,7 +1200,7 @@
         <v>1.001986754966887</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.001261431725008</v>
+        <v>1.00157678965626</v>
       </c>
     </row>
     <row r="13">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-52</v>
+        <v>-43</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>53</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -1210,79 +1210,79 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>-43</v>
+        <v>-31</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E13" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>-67</v>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>-56</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>-33</v>
+      </c>
+      <c r="K13" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="L13" s="10" t="n">
+        <v>-21</v>
+      </c>
+      <c r="M13" s="10" t="n">
+        <v>-55</v>
+      </c>
+      <c r="N13" s="10" t="n">
         <v>63</v>
       </c>
-      <c r="F13" s="10" t="n">
-        <v>-74</v>
-      </c>
-      <c r="G13" s="10" t="n">
-        <v>-54</v>
-      </c>
-      <c r="H13" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="I13" s="10" t="n">
-        <v>74</v>
-      </c>
-      <c r="J13" s="10" t="n">
-        <v>-34</v>
-      </c>
-      <c r="K13" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="L13" s="10" t="n">
-        <v>-19</v>
-      </c>
-      <c r="M13" s="10" t="n">
-        <v>-51</v>
-      </c>
-      <c r="N13" s="10" t="n">
-        <v>60</v>
-      </c>
       <c r="O13" s="10" t="n">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="P13" s="10" t="n">
         <v>61</v>
       </c>
       <c r="Q13" s="10" t="n">
-        <v>-96</v>
+        <v>-92</v>
       </c>
       <c r="R13" s="10" t="n">
         <v>65</v>
       </c>
       <c r="S13" s="10" t="n">
-        <v>-57</v>
+        <v>-52</v>
       </c>
       <c r="T13" s="10" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="U13" s="10" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="V13" s="10" t="n">
-        <v>-30</v>
+        <v>-28</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-96</v>
+        <v>-92</v>
       </c>
       <c r="X13" s="10" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="Y13" s="11" t="n">
         <v>6</v>
       </c>
       <c r="Z13" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>86</v>
@@ -1301,19 +1301,19 @@
         <v>78</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G14" s="5" t="n">
         <v>73</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J14" s="5" t="n">
         <v>72</v>
@@ -1322,16 +1322,16 @@
         <v>78</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M14" s="5" t="n">
         <v>70</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P14" s="5" t="n">
         <v>86</v>
@@ -1343,10 +1343,10 @@
         <v>77</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="U14" s="5" t="n">
         <v>81</v>
@@ -1358,7 +1358,7 @@
         <v>65</v>
       </c>
       <c r="X14" s="5" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Y14" s="12" t="n">
         <v>77</v>

--- a/outputs/historical_hdd_thresholds.xlsx
+++ b/outputs/historical_hdd_thresholds.xlsx
@@ -515,109 +515,109 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>2013</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="Q3" s="3" t="inlineStr">
+      <c r="R3" s="3" t="inlineStr">
         <is>
           <t>2011</t>
         </is>
       </c>
-      <c r="R3" s="3" t="inlineStr">
+      <c r="S3" s="3" t="inlineStr">
         <is>
           <t>2010</t>
         </is>
       </c>
-      <c r="S3" s="3" t="inlineStr">
+      <c r="T3" s="3" t="inlineStr">
         <is>
           <t>2009</t>
         </is>
       </c>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="U3" s="3" t="inlineStr">
         <is>
           <t>2008</t>
         </is>
       </c>
-      <c r="U3" s="3" t="inlineStr">
+      <c r="V3" s="3" t="inlineStr">
         <is>
           <t>2007</t>
         </is>
       </c>
-      <c r="V3" s="3" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
           <t>Min</t>
@@ -630,7 +630,7 @@
       </c>
       <c r="Y3" s="4" t="inlineStr">
         <is>
-          <t>Average (2015-2024)</t>
+          <t>Average (2016-2025)</t>
         </is>
       </c>
       <c r="Z3" s="3" t="inlineStr">
@@ -890,11 +890,11 @@
         <v>28</v>
       </c>
       <c r="D7" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="E7" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="E7" s="5" t="n">
-        <v>28</v>
-      </c>
       <c r="F7" s="5" t="n">
         <v>28</v>
       </c>
@@ -902,11 +902,11 @@
         <v>28</v>
       </c>
       <c r="H7" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="I7" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="I7" s="5" t="n">
-        <v>28</v>
-      </c>
       <c r="J7" s="5" t="n">
         <v>28</v>
       </c>
@@ -914,11 +914,11 @@
         <v>28</v>
       </c>
       <c r="L7" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="M7" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="M7" s="5" t="n">
-        <v>28</v>
-      </c>
       <c r="N7" s="5" t="n">
         <v>28</v>
       </c>
@@ -926,11 +926,11 @@
         <v>28</v>
       </c>
       <c r="P7" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q7" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="Q7" s="5" t="n">
-        <v>28</v>
-      </c>
       <c r="R7" s="5" t="n">
         <v>28</v>
       </c>
@@ -938,10 +938,10 @@
         <v>28</v>
       </c>
       <c r="T7" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="U7" s="5" t="n">
         <v>29</v>
-      </c>
-      <c r="U7" s="5" t="n">
-        <v>28</v>
       </c>
       <c r="V7" s="5" t="n">
         <v>28</v>
@@ -1052,11 +1052,11 @@
         <v>151</v>
       </c>
       <c r="D9" s="7" t="n">
+        <v>151</v>
+      </c>
+      <c r="E9" s="7" t="n">
         <v>152</v>
       </c>
-      <c r="E9" s="7" t="n">
-        <v>151</v>
-      </c>
       <c r="F9" s="7" t="n">
         <v>151</v>
       </c>
@@ -1064,11 +1064,11 @@
         <v>151</v>
       </c>
       <c r="H9" s="7" t="n">
+        <v>151</v>
+      </c>
+      <c r="I9" s="7" t="n">
         <v>152</v>
       </c>
-      <c r="I9" s="7" t="n">
-        <v>151</v>
-      </c>
       <c r="J9" s="7" t="n">
         <v>151</v>
       </c>
@@ -1076,11 +1076,11 @@
         <v>151</v>
       </c>
       <c r="L9" s="7" t="n">
+        <v>151</v>
+      </c>
+      <c r="M9" s="7" t="n">
         <v>152</v>
       </c>
-      <c r="M9" s="7" t="n">
-        <v>151</v>
-      </c>
       <c r="N9" s="7" t="n">
         <v>151</v>
       </c>
@@ -1088,11 +1088,11 @@
         <v>151</v>
       </c>
       <c r="P9" s="7" t="n">
+        <v>151</v>
+      </c>
+      <c r="Q9" s="7" t="n">
         <v>152</v>
       </c>
-      <c r="Q9" s="7" t="n">
-        <v>151</v>
-      </c>
       <c r="R9" s="7" t="n">
         <v>151</v>
       </c>
@@ -1100,10 +1100,10 @@
         <v>151</v>
       </c>
       <c r="T9" s="7" t="n">
+        <v>151</v>
+      </c>
+      <c r="U9" s="7" t="n">
         <v>152</v>
-      </c>
-      <c r="U9" s="7" t="n">
-        <v>151</v>
       </c>
       <c r="V9" s="7" t="n">
         <v>151</v>
@@ -1197,7 +1197,7 @@
         <v>1.006622516556291</v>
       </c>
       <c r="Y10" s="8" t="n">
-        <v>1.001986754966887</v>
+        <v>1.001324503311258</v>
       </c>
       <c r="Z10" s="8" t="n">
         <v>1.00157678965626</v>
@@ -1216,10 +1216,10 @@
         <v>49</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F13" s="10" t="n">
         <v>-67</v>
@@ -1228,10 +1228,10 @@
         <v>-56</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J13" s="10" t="n">
         <v>-33</v>
@@ -1240,10 +1240,10 @@
         <v>29</v>
       </c>
       <c r="L13" s="10" t="n">
-        <v>-21</v>
+        <v>-20</v>
       </c>
       <c r="M13" s="10" t="n">
-        <v>-55</v>
+        <v>-56</v>
       </c>
       <c r="N13" s="10" t="n">
         <v>63</v>
@@ -1252,10 +1252,10 @@
         <v>-17</v>
       </c>
       <c r="P13" s="10" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q13" s="10" t="n">
-        <v>-92</v>
+        <v>-98</v>
       </c>
       <c r="R13" s="10" t="n">
         <v>65</v>
@@ -1264,7 +1264,7 @@
         <v>-52</v>
       </c>
       <c r="T13" s="10" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="U13" s="10" t="n">
         <v>59</v>
@@ -1273,10 +1273,10 @@
         <v>-28</v>
       </c>
       <c r="W13" s="10" t="n">
-        <v>-92</v>
+        <v>-98</v>
       </c>
       <c r="X13" s="10" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y13" s="11" t="n">
         <v>6</v>
@@ -1298,10 +1298,10 @@
         <v>86</v>
       </c>
       <c r="D14" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="E14" s="5" t="n">
         <v>78</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>77</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>69</v>
